--- a/output/ord-To_add.xlsx
+++ b/output/ord-To_add.xlsx
@@ -524,11 +524,13 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>raggio cx-ray sapim 244mm straight pull nero</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>710845688461</v>
+          <t>CERAMICSPEED accessorio gabbia cambio OSPW con pulegge carbonio 11 velocità rosso custom</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CS02GCW35000055M</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -541,13 +543,13 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>17</v>
+        <v>459</v>
       </c>
       <c r="O2" t="n">
-        <v>9.9</v>
+        <v>275.4</v>
       </c>
       <c r="P2" t="n">
-        <v>7.53</v>
+        <v>275.4</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>

--- a/output/ord-To_add.xlsx
+++ b/output/ord-To_add.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,96 +413,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CODICE INTERNO</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DESCRIZIONE INTERNA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Codice-a-barre</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>UM</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MERCEOLOGICO</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>FAMIGLIA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>CONTROPARTITA CONTABILE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>TIPOLOGIA RAEE</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>CODICE PRODUTTORE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>BARCODE PRODUTTORE</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PREZZO PRODUTTORE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>PREZZO</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>SCONTI</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>PUBBLICO</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>PREZZO-VENDITA</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>PREZZO-ACQUISTO</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Peso-lordo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
@@ -554,6 +542,918 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SRAM accessorio distanziale sterzo carbonio 2x2,5mm 1x5mm 1x10mm 1x20mm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>710845841118</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>00.4318.035.001</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>22</v>
+      </c>
+      <c r="O3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SRAM cp.pulegge gx1 eagle 12v e Apex eagle 12v</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>710845812859</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>11.7518.089.000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>40</v>
+      </c>
+      <c r="O4" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SRAM pastiglie LEVEL TLM/ULTM RED/FORCE 1pz RED22/FORCE22/RIVAL/APEX ACCIAIO ORGANICHE 20 pezzi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>710845781377</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>11.5018.037.000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>237</v>
+      </c>
+      <c r="O5" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SRAM accessorio etap caricabatteria</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>710845780752</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>00.3018.117.000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>52</v>
+      </c>
+      <c r="O6" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 30 course tubolare anteriore+posteriore disco shimano</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3548720109651</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>146055</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>1023</v>
+      </c>
+      <c r="O7" t="n">
+        <v>606</v>
+      </c>
+      <c r="P7" t="n">
+        <v>606</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 30 course copertoncino anteriore+posteriore disco shimano</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3548720109645</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>146054</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>1023</v>
+      </c>
+      <c r="O8" t="n">
+        <v>606</v>
+      </c>
+      <c r="P8" t="n">
+        <v>606</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 302 copertoncino anteriore+posteriore nero 2019 shimano</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3548720109812</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>242233</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>1534</v>
+      </c>
+      <c r="O9" t="n">
+        <v>896</v>
+      </c>
+      <c r="P9" t="n">
+        <v>896</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 404 copertoncino anteriore+posteriore nero 2019 shimano</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3548720109752</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>242114</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1382</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1382</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 404 copertoncino anteriore+posteriore bianco 2019 shimano</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3548720109746</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>242113</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1382</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1382</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 808 copertoncino anteriore+posteriore nero 2019 shimano</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3548720109764</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>242116</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>2600</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1625</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1625</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 858 NSW copertoncino anteriore+posteriore disco shimano</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3548720109800</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>242231</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>3200</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2134</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2134</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 454 NSW copertoncino anteriore+posteriore disco shimano</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3548720109716</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>215523</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2680</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2680</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 303 tubolare anteriore+posteriore nero 2019 shimano</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3548720109728</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>242110</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1382</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1382</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 404 NSW copertoncino anteriore+posteriore disco shimano</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3548720109824</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>242246</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 303 copertoncino anteriore+posteriore nero 2019 shimano</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3548720109740</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>242112</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1382</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1382</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 303 copertoncino anteriore+posteriore bianco 2019 shimano</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3548720109734</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>242111</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1382</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1382</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 303 NSW copertoncino anteriore+posteriore shimano</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3548720109770</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3548720109770</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 202 copertoncino anteriore+posteriore nero 2019 shimano</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3548720109675</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>146059</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1382</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1382</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 302 copertoncino anteriore+posteriore bianco 2019 shimano</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3548720109681</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>210968</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>1534</v>
+      </c>
+      <c r="O21" t="n">
+        <v>896</v>
+      </c>
+      <c r="P21" t="n">
+        <v>896</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 302 copertoncino anteriore+posteriore disco nero 2019 shimano</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3548720109878</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>242256</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>1534</v>
+      </c>
+      <c r="O22" t="n">
+        <v>896</v>
+      </c>
+      <c r="P22" t="n">
+        <v>896</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 858 NSW copertoncino anteriore+posteriore shimano</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3548720109794</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>242121</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>3200</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2134</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2134</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 202 NSW copertoncino anteriore+posteriore shimano</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3548720109710</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>215522</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>2688</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1853</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1853</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 302 copertoncino anteriore+posteriore disco bianco 2019 shimano</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3548720109704</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>210970</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>1534</v>
+      </c>
+      <c r="O25" t="n">
+        <v>896</v>
+      </c>
+      <c r="P25" t="n">
+        <v>896</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ZIPP ruote 303 tubolare anteriore+posteriore bianco 2019 shimano</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3548720109722</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>242109</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1382</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1382</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
